--- a/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 0,0</t>
+          <t>-74,35; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 37,33</t>
+          <t>-45,25; 37,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 0,0</t>
+          <t>-74,35; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 67,82</t>
+          <t>-52,53; 69,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 9,63</t>
+          <t>-9,59; 8,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 6,93</t>
+          <t>-13,47; 7,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 11,82</t>
+          <t>-10,08; 10,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 9,39</t>
+          <t>-10,22; 11,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 12,3</t>
+          <t>-10,82; 11,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 9,11</t>
+          <t>-15,49; 9,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 15,56</t>
+          <t>-11,8; 14,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 11,69</t>
+          <t>-11,74; 14,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 0,29</t>
+          <t>-20,83; -1,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 10,81</t>
+          <t>-8,14; 10,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 2,85</t>
+          <t>-12,93; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 8,58</t>
+          <t>-10,75; 7,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 0,61</t>
+          <t>-24,62; -1,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 15,89</t>
+          <t>-10,28; 14,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 3,66</t>
+          <t>-16,38; 3,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 11,17</t>
+          <t>-12,59; 8,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 3,06</t>
+          <t>-13,97; 3,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 0,26</t>
+          <t>-16,72; 0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 9,15</t>
+          <t>-9,4; 8,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 6,91</t>
+          <t>-7,82; 6,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 5,53</t>
+          <t>-21,89; 5,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 0,25</t>
+          <t>-21,3; 0,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 14,43</t>
+          <t>-12,94; 13,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 9,05</t>
+          <t>-9,21; 8,41</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 0,12</t>
+          <t>-11,19; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,63</t>
+          <t>-9,38; 0,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,89</t>
+          <t>-7,32; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,52</t>
+          <t>-5,38; 4,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,12</t>
+          <t>-15,04; 0,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,29</t>
+          <t>-11,88; 1,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,96</t>
+          <t>-9,33; 4,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,69</t>
+          <t>-6,28; 5,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 0,0</t>
+          <t>-71,91; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 37,47</t>
+          <t>-46,44; 38,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 0,0</t>
+          <t>-71,91; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 69,0</t>
+          <t>-51,74; 69,77</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 8,9</t>
+          <t>-8,92; 9,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 7,19</t>
+          <t>-12,84; 6,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 10,94</t>
+          <t>-11,04; 11,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 11,49</t>
+          <t>-11,11; 9,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 11,27</t>
+          <t>-10,05; 12,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 9,4</t>
+          <t>-15,1; 8,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 14,84</t>
+          <t>-12,85; 15,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 14,96</t>
+          <t>-12,49; 12,47</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -1,12</t>
+          <t>-19,79; -0,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 10,23</t>
+          <t>-7,36; 11,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 2,97</t>
+          <t>-13,46; 2,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 7,03</t>
+          <t>-10,62; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,62; -1,49</t>
+          <t>-23,74; -0,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 14,6</t>
+          <t>-9,49; 16,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 3,55</t>
+          <t>-16,18; 3,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 8,94</t>
+          <t>-12,37; 10,47</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 3,25</t>
+          <t>-13,79; 3,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 0,52</t>
+          <t>-16,77; 0,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 8,91</t>
+          <t>-9,17; 9,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 6,47</t>
+          <t>-7,97; 7,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 5,88</t>
+          <t>-21,47; 5,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 0,75</t>
+          <t>-21,63; 0,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 13,6</t>
+          <t>-12,48; 14,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 8,41</t>
+          <t>-9,37; 9,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 0,11</t>
+          <t>-10,88; -0,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,99</t>
+          <t>-9,08; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,1</t>
+          <t>-7,85; 2,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,11</t>
+          <t>-5,83; 3,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 0,17</t>
+          <t>-14,73; -0,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 1,32</t>
+          <t>-11,64; 2,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,2</t>
+          <t>-9,8; 3,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,12</t>
+          <t>-7,0; 4,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,1%</t>
+          <t>-1,5%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 0,0</t>
+          <t>-77,02; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 38,08</t>
+          <t>-42,08; 35,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 0,0</t>
+          <t>-77,02; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 69,77</t>
+          <t>-46,38; 64,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,08%</t>
+          <t>-2,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 9,99</t>
+          <t>-9,65; 9,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 6,71</t>
+          <t>-12,61; 6,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 11,51</t>
+          <t>-11,07; 11,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 9,7</t>
+          <t>-13,13; 8,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 12,41</t>
+          <t>-10,88; 12,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 8,77</t>
+          <t>-14,97; 9,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 15,4</t>
+          <t>-12,9; 15,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 12,47</t>
+          <t>-14,59; 10,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,79; -0,73</t>
+          <t>-19,26; 0,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 11,58</t>
+          <t>-6,44; 10,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 2,71</t>
+          <t>-13,29; 2,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 8,18</t>
+          <t>-6,88; 9,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,74; -0,86</t>
+          <t>-22,84; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 16,86</t>
+          <t>-8,21; 15,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 3,67</t>
+          <t>-16,06; 3,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 10,47</t>
+          <t>-8,04; 12,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,02%</t>
+          <t>-1,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 3,07</t>
+          <t>-13,73; 3,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 0,12</t>
+          <t>-17,11; 0,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 9,4</t>
+          <t>-8,94; 9,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 7,27</t>
+          <t>-8,64; 6,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 5,26</t>
+          <t>-21,81; 5,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 0,17</t>
+          <t>-21,76; 0,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 14,57</t>
+          <t>-11,8; 14,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 9,29</t>
+          <t>-10,21; 7,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,9%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,03</t>
+          <t>-10,68; 0,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,67</t>
+          <t>-8,99; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,65</t>
+          <t>-7,57; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,9</t>
+          <t>-5,21; 4,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -0,15</t>
+          <t>-14,6; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 2,24</t>
+          <t>-11,43; 2,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 3,68</t>
+          <t>-9,64; 3,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,86</t>
+          <t>-6,15; 5,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-19,67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-37,86</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-19,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-37,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-1,5%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-19.67435395173791</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-37.86172778250603</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.160765662306518</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1967435395173791</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3786172778250603</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.01503454551500668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-77,02; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-42,08; 35,84</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-77,02; 0,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-46,38; 64,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-77.01644129621388</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-42.08334274696291</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7701644129621388</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.4638121270673393</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>35.84294772003962</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>0.6478287994730473</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,13</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-9,65; 9,63</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-12,61; 6,93</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,07; 11,82</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-13,13; 8,04</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-10,88; 12,3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-14,97; 9,11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-12,9; 15,56</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-14,59; 10,22</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5900455373240354</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.74071724563496</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4399916681163907</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.126958437931659</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.006980568095993356</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03371058234756101</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.005501915829460116</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.0251091209480254</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-9,94</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-12,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-6,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-9.646426587200125</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-12.60873539690025</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-11.07282244148336</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-13.12624372964983</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1087838792536108</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1497455092535125</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1289564127284125</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1459335187505576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-19,26; 0,29</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,44; 10,81</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,29; 2,85</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,88; 9,99</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-22,84; 0,61</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-8,21; 15,89</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-16,06; 3,66</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-8,04; 12,76</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.627904717382311</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.929576141369593</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.82008920013873</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.038700629280422</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1229890412541585</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.09106693170376899</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.155597174188122</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1022072718783825</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +803,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-8,69</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-11,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-0,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-1,74%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-9.937488064909417</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.004703577524158</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.770716454405011</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.307845092938764</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1236298692797057</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.02750551902078626</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.06035851614792301</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.01589790319851918</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-13,73; 3,06</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-17,11; 0,26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 9,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 6,22</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-21,81; 5,53</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-21,76; 0,25</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-11,8; 14,43</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-10,21; 7,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-19.25777348764358</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.437525655584809</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.2859909130226</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.876346234962572</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2283692770737278</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.08213430344029313</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1606326275244411</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.0803912530194564</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.288938316160385</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.81100158965017</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.853286210721778</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.994193911349058</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.00609354380616004</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1589030731653499</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.03656523183746877</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.127587686468685</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.43349772400129</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-8.69320890539792</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2688183312909209</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.433969912347355</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.09129999553753755</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1155055314345992</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.003850608583604671</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.01743805600939533</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-13.72514403593649</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-17.10840294655905</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-8.942795098513736</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.637817569927524</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2180937990769785</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2175505525046068</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1180150393823636</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1020931658542651</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.05511527157245</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2559339389130273</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.146345429815122</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.219132272342744</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.05526352127815062</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.002540513841196994</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1443373929784328</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.07831128765200979</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-5,21</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,85</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-5,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,68; 0,12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; 1,63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,57; 2,89</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; 4,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-14,6; 0,12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-11,43; 2,29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-9,64; 3,96</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-6,15; 5,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-5.212416755683913</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-3.847131579083996</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.346113532139593</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.6911477863691395</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.0730189106317876</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.0506364186767898</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.03090186111261805</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.008371939748779599</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.68446303506486</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.989965860777467</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.569255816311143</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.20983897919485</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1460294691063848</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1142622404113307</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.09636095031837134</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.06145701801176513</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1205785602458333</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.633280847582105</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.890588730925806</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.707408935664438</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.001174760394097873</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.02290626049578703</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.03962332347630908</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.05865344595378109</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1101,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
